--- a/data/trans_orig/P36BPD13_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD13_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas en 2023</t>
+          <t>Población según si consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>408954</t>
+          <t>407011</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>441606</t>
+          <t>440414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>391436</t>
+          <t>391678</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>411554</t>
+          <t>411354</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>808700</t>
+          <t>808456</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>846776</t>
+          <t>846664</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,5%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60768</t>
+          <t>61960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93420</t>
+          <t>95363</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32113</t>
+          <t>32313</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52231</t>
+          <t>51989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99265</t>
+          <t>99377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137341</t>
+          <t>137585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>354749</t>
+          <t>356697</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>390531</t>
+          <t>389389</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>323178</t>
+          <t>324055</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>344394</t>
+          <t>344585</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>686397</t>
+          <t>685969</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>728619</t>
+          <t>725658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57898</t>
+          <t>59040</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93680</t>
+          <t>91732</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34114</t>
+          <t>33923</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55330</t>
+          <t>54453</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98318</t>
+          <t>101279</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140540</t>
+          <t>140968</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>541369</t>
+          <t>539696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>641064</t>
+          <t>635318</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>135943</t>
+          <t>135789</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150989</t>
+          <t>150467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>688416</t>
+          <t>688066</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>789181</t>
+          <t>790193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22787</t>
+          <t>28533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>122482</t>
+          <t>124155</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27949</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>37549</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139326</t>
+          <t>139676</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>845623</t>
+          <t>844671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>898789</t>
+          <t>896942</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>832224</t>
+          <t>834995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>920945</t>
+          <t>930748</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1695162</t>
+          <t>1694968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1824615</t>
+          <t>1819759</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>131195</t>
+          <t>133042</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>184361</t>
+          <t>185313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54065</t>
+          <t>44262</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142786</t>
+          <t>140015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>180380</t>
+          <t>185236</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309833</t>
+          <t>310027</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>368657</t>
+          <t>367067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>405021</t>
+          <t>403795</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>735027</t>
+          <t>733258</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>776724</t>
+          <t>778435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1116439</t>
+          <t>1115151</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1173105</t>
+          <t>1173139</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65933</t>
+          <t>67159</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102297</t>
+          <t>103887</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61240</t>
+          <t>59529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102937</t>
+          <t>104706</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>135813</t>
+          <t>135779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>192479</t>
+          <t>193767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>199911</t>
+          <t>200149</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>231272</t>
+          <t>229971</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>640922</t>
+          <t>639216</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>676079</t>
+          <t>675449</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>851857</t>
+          <t>850358</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>899739</t>
+          <t>899681</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40596</t>
+          <t>40358</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80706</t>
+          <t>81336</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>115863</t>
+          <t>117569</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97553</t>
+          <t>97611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145435</t>
+          <t>146934</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2810931</t>
+          <t>2808061</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2981709</t>
+          <t>2970217</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3116725</t>
+          <t>3114505</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3232566</t>
+          <t>3233774</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5948717</t>
+          <t>5949331</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6175010</t>
+          <t>6150719</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>374390</t>
+          <t>385882</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>545168</t>
+          <t>548038</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>323260</t>
+          <t>322052</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>439101</t>
+          <t>441321</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>736915</t>
+          <t>761206</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>963208</t>
+          <t>962594</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD13_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD13_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>426142</t>
+          <t>467801</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>407011</t>
+          <t>450786</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>440414</t>
+          <t>483515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>402688</t>
+          <t>436674</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>391678</t>
+          <t>424023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>411354</t>
+          <t>446765</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>828830</t>
+          <t>904475</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>808456</t>
+          <t>882994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>846664</t>
+          <t>923972</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,55%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76232</t>
+          <t>79924</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61960</t>
+          <t>64210</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95363</t>
+          <t>96939</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40979</t>
+          <t>47392</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32313</t>
+          <t>37301</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51989</t>
+          <t>60043</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>117211</t>
+          <t>127316</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99377</t>
+          <t>107819</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137585</t>
+          <t>148797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>502374</t>
+          <t>547725</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>502374</t>
+          <t>547725</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>502374</t>
+          <t>547725</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>443667</t>
+          <t>484066</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>443667</t>
+          <t>484066</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>443667</t>
+          <t>484066</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>946041</t>
+          <t>1031791</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>946041</t>
+          <t>1031791</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>946041</t>
+          <t>1031791</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>373292</t>
+          <t>400405</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>356697</t>
+          <t>380478</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>389389</t>
+          <t>416363</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>334726</t>
+          <t>368047</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>324055</t>
+          <t>355337</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>344585</t>
+          <t>378307</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>708018</t>
+          <t>768452</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>685969</t>
+          <t>745254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>725658</t>
+          <t>789773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,03%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>75137</t>
+          <t>78185</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59040</t>
+          <t>62227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91732</t>
+          <t>98112</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43782</t>
+          <t>50484</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33923</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54453</t>
+          <t>63194</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>118919</t>
+          <t>128669</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101279</t>
+          <t>107348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140968</t>
+          <t>151867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>448429</t>
+          <t>478590</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>448429</t>
+          <t>478590</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>448429</t>
+          <t>478590</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>378508</t>
+          <t>418531</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>378508</t>
+          <t>418531</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>378508</t>
+          <t>418531</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>826937</t>
+          <t>897121</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>826937</t>
+          <t>897121</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>826937</t>
+          <t>897121</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>591076</t>
+          <t>387299</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>539696</t>
+          <t>369047</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>635318</t>
+          <t>404713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>144255</t>
+          <t>161778</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>135789</t>
+          <t>151666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150467</t>
+          <t>168511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>735330</t>
+          <t>549077</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>688066</t>
+          <t>529796</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>790193</t>
+          <t>567601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>87,19%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72775</t>
+          <t>79961</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>62547</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124155</t>
+          <t>98213</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19637</t>
+          <t>21970</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28103</t>
+          <t>32082</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>92412</t>
+          <t>101931</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37549</t>
+          <t>83407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139676</t>
+          <t>121212</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>663851</t>
+          <t>467260</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>663851</t>
+          <t>467260</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>663851</t>
+          <t>467260</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>163892</t>
+          <t>183748</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>163892</t>
+          <t>183748</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>163892</t>
+          <t>183748</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>827742</t>
+          <t>651008</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>827742</t>
+          <t>651008</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>827742</t>
+          <t>651008</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>873174</t>
+          <t>954086</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>844671</t>
+          <t>921910</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>896942</t>
+          <t>978110</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>869232</t>
+          <t>741568</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>834995</t>
+          <t>722043</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>930748</t>
+          <t>759774</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1742407</t>
+          <t>1695654</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1694968</t>
+          <t>1660748</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1819759</t>
+          <t>1728453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>87,1%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>156810</t>
+          <t>172162</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133042</t>
+          <t>148138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185313</t>
+          <t>204338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>105778</t>
+          <t>116632</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44262</t>
+          <t>98426</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140015</t>
+          <t>136157</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>262588</t>
+          <t>288794</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>185236</t>
+          <t>255995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310027</t>
+          <t>323700</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1029984</t>
+          <t>1126248</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1029984</t>
+          <t>1126248</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1029984</t>
+          <t>1126248</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>975010</t>
+          <t>858200</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>975010</t>
+          <t>858200</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>975010</t>
+          <t>858200</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2004995</t>
+          <t>1984448</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2004995</t>
+          <t>1984448</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2004995</t>
+          <t>1984448</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>388131</t>
+          <t>472413</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>367067</t>
+          <t>451712</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>403795</t>
+          <t>490913</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>753128</t>
+          <t>728761</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>733258</t>
+          <t>712514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>778435</t>
+          <t>744211</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1141259</t>
+          <t>1201174</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1115151</t>
+          <t>1174644</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1173139</t>
+          <t>1225386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82823</t>
+          <t>91764</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67159</t>
+          <t>73264</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>103887</t>
+          <t>112465</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>84836</t>
+          <t>97611</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59529</t>
+          <t>82161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104706</t>
+          <t>113858</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>167659</t>
+          <t>189375</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>135779</t>
+          <t>165163</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>193767</t>
+          <t>215905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>470954</t>
+          <t>564177</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>470954</t>
+          <t>564177</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>470954</t>
+          <t>564177</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>837964</t>
+          <t>826372</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837964</t>
+          <t>826372</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>837964</t>
+          <t>826372</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1308918</t>
+          <t>1390549</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1308918</t>
+          <t>1390549</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1308918</t>
+          <t>1390549</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>218531</t>
+          <t>214339</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>200149</t>
+          <t>195569</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>229971</t>
+          <t>224760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>658719</t>
+          <t>729041</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>639216</t>
+          <t>705741</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>675449</t>
+          <t>745912</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>877250</t>
+          <t>943380</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>850358</t>
+          <t>915234</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>899681</t>
+          <t>966022</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21976</t>
+          <t>22889</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>12468</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40358</t>
+          <t>41659</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>98066</t>
+          <t>110144</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>81336</t>
+          <t>93273</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117569</t>
+          <t>133444</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>120042</t>
+          <t>133033</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97611</t>
+          <t>110391</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146934</t>
+          <t>161179</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>756785</t>
+          <t>839185</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>756785</t>
+          <t>839185</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>756785</t>
+          <t>839185</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>997292</t>
+          <t>1076413</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>997292</t>
+          <t>1076413</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>997292</t>
+          <t>1076413</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2870345</t>
+          <t>2896343</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2808061</t>
+          <t>2845239</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2970217</t>
+          <t>2942092</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3162747</t>
+          <t>3165868</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3114505</t>
+          <t>3131794</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3233774</t>
+          <t>3204268</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6033092</t>
+          <t>6062211</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5949331</t>
+          <t>6001156</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6150719</t>
+          <t>6121061</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>87,05%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>485754</t>
+          <t>524886</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>385882</t>
+          <t>479137</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>548038</t>
+          <t>575990</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>393079</t>
+          <t>444233</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>322052</t>
+          <t>405833</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>441321</t>
+          <t>478307</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>878833</t>
+          <t>969119</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>761206</t>
+          <t>910269</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>962594</t>
+          <t>1030174</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3356099</t>
+          <t>3421229</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3356099</t>
+          <t>3421229</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3356099</t>
+          <t>3421229</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3555826</t>
+          <t>3610101</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3555826</t>
+          <t>3610101</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3555826</t>
+          <t>3610101</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6911925</t>
+          <t>7031330</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6911925</t>
+          <t>7031330</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6911925</t>
+          <t>7031330</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
